--- a/Hydroacoustics/TAST/Seal_presence_time_TAST_OFF_KH.xlsx
+++ b/Hydroacoustics/TAST/Seal_presence_time_TAST_OFF_KH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khomolka\Documents\GitHub\PGST-Natural-Resources\Hydroacoustics\TAST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15790521-1CAC-4978-BCCB-35E59E2CE45D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB20203-E2F4-4207-AC0A-827885249C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E8DB433E-2EA1-4194-92B6-EDDC73B0D35C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E8DB433E-2EA1-4194-92B6-EDDC73B0D35C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="443">
   <si>
     <t>Notes</t>
   </si>
@@ -152,9 +152,6 @@
     <t>May_24_2023_144714_2476</t>
   </si>
   <si>
-    <t>Large seal in for small amount of time but looks like smaller seals are in for larger duration</t>
-  </si>
-  <si>
     <t>May_24_2023_144714_2477</t>
   </si>
   <si>
@@ -365,9 +362,6 @@
     <t xml:space="preserve">High number of fish, seal or multiple seals are swimming through school then floating for a bit. </t>
   </si>
   <si>
-    <t>interesting mom and babies?</t>
-  </si>
-  <si>
     <t>Jun_21_2023_145422_8</t>
   </si>
   <si>
@@ -1368,6 +1362,9 @@
   </si>
   <si>
     <t>Time_Out_2</t>
+  </si>
+  <si>
+    <t>Large seal in for small amount of time but looks like smaller seals are in for larger duration; interesting mom and babies?</t>
   </si>
 </sst>
 </file>
@@ -1761,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3A6E59-FEDB-4A97-ACEB-6EC8499C57A1}">
-  <dimension ref="A1:T334"/>
+  <dimension ref="A1:S334"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1782,64 +1779,64 @@
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="152.7109375" customWidth="1"/>
     <col min="20" max="39" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="O1" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>432</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="M1" s="13" t="s">
+      <c r="P1" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q1" t="s">
         <v>437</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="R1" t="s">
         <v>438</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="P1" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>439</v>
-      </c>
-      <c r="R1" t="s">
-        <v>440</v>
       </c>
       <c r="S1" t="s">
         <v>0</v>
@@ -1867,10 +1864,10 @@
         <v>77.700000000000642</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="S2" t="s">
         <v>2</v>
@@ -1898,10 +1895,10 @@
         <v>5.7000000000037687</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="S3" t="s">
         <v>4</v>
@@ -1929,10 +1926,10 @@
         <v>9.6000000000053376</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>6</v>
@@ -1960,10 +1957,10 @@
         <v>23.300000000003962</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="S5" t="s">
         <v>8</v>
@@ -1991,10 +1988,10 @@
         <v>65.700000000003556</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="S6" t="s">
         <v>11</v>
@@ -2022,10 +2019,10 @@
         <v>23.000000000006793</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S7" t="s">
         <v>12</v>
@@ -2053,10 +2050,10 @@
         <v>43.000000000003524</v>
       </c>
       <c r="Q8" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S8" t="s">
         <v>14</v>
@@ -2084,10 +2081,10 @@
         <v>21.400000000000208</v>
       </c>
       <c r="Q9" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S9" t="s">
         <v>16</v>
@@ -2115,10 +2112,10 @@
         <v>56.200000000000074</v>
       </c>
       <c r="Q10" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S10" t="s">
         <v>18</v>
@@ -2146,10 +2143,10 @@
         <v>16.900000000000404</v>
       </c>
       <c r="Q11" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S11" t="s">
         <v>20</v>
@@ -2177,10 +2174,10 @@
         <v>4.8000000000002707</v>
       </c>
       <c r="Q12" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S12" t="s">
         <v>22</v>
@@ -2208,10 +2205,10 @@
         <v>13.299999999998402</v>
       </c>
       <c r="Q13" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S13" t="s">
         <v>24</v>
@@ -2239,10 +2236,10 @@
         <v>48.899999999999011</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>26</v>
@@ -2270,10 +2267,10 @@
         <v>4.6999999999972175</v>
       </c>
       <c r="Q15" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S15" t="s">
         <v>28</v>
@@ -2301,16 +2298,16 @@
         <v>28.599999999995518</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2332,16 +2329,16 @@
         <v>44.900000000001583</v>
       </c>
       <c r="Q17" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R17" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="S17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -2363,16 +2360,16 @@
         <v>16.200000000000614</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S18" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2394,16 +2391,16 @@
         <v>45.000000000007034</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -2425,21 +2422,18 @@
         <v>12.100000000000133</v>
       </c>
       <c r="Q20" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R20" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S20" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>38</v>
-      </c>
-      <c r="T20" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>39</v>
       </c>
       <c r="B21" s="7">
         <v>45083</v>
@@ -2465,18 +2459,18 @@
         <v>43.300000000000097</v>
       </c>
       <c r="Q21" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R21" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>41</v>
       </c>
       <c r="B22" s="7">
         <v>45083</v>
@@ -2496,18 +2490,18 @@
         <v>15.599999999999682</v>
       </c>
       <c r="Q22" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R22" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>43</v>
       </c>
       <c r="B23" s="7">
         <v>45083</v>
@@ -2527,18 +2521,18 @@
         <v>26.89999999999997</v>
       </c>
       <c r="Q23" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R23" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="7">
         <v>45083</v>
@@ -2564,18 +2558,18 @@
         <v>63.700000000000045</v>
       </c>
       <c r="Q24" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>47</v>
       </c>
       <c r="B25" s="7">
         <v>45083</v>
@@ -2601,18 +2595,18 @@
         <v>14.69999999999918</v>
       </c>
       <c r="Q25" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R25" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>49</v>
       </c>
       <c r="B26" s="7">
         <v>45083</v>
@@ -2632,18 +2626,18 @@
         <v>6.8000000000001837</v>
       </c>
       <c r="Q26" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R26" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R26" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>51</v>
       </c>
       <c r="B27" s="7">
         <v>45083</v>
@@ -2663,18 +2657,18 @@
         <v>9.4000000000004302</v>
       </c>
       <c r="Q27" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R27" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R27" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>53</v>
       </c>
       <c r="B28" s="7">
         <v>45083</v>
@@ -2688,18 +2682,18 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S28" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>55</v>
       </c>
       <c r="B29" s="7">
         <v>45083</v>
@@ -2725,18 +2719,18 @@
         <v>32.999999999995566</v>
       </c>
       <c r="Q29" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R29" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R29" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>57</v>
       </c>
       <c r="B30" s="7">
         <v>45083</v>
@@ -2756,18 +2750,18 @@
         <v>12.299999999999045</v>
       </c>
       <c r="Q30" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R30" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>59</v>
       </c>
       <c r="B31" s="7">
         <v>45084</v>
@@ -2787,18 +2781,18 @@
         <v>18.799999999998462</v>
       </c>
       <c r="Q31" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R31" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>61</v>
       </c>
       <c r="B32" s="7">
         <v>45084</v>
@@ -2818,18 +2812,18 @@
         <v>11.300000000002086</v>
       </c>
       <c r="Q32" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R32" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R32" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B33" s="7">
         <v>45084</v>
@@ -2855,18 +2849,18 @@
         <v>31.400000000013861</v>
       </c>
       <c r="Q33" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R33" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R33" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="7">
         <v>45084</v>
@@ -2892,18 +2886,18 @@
         <v>35.800000000004317</v>
       </c>
       <c r="Q34" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R34" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B35" s="7">
         <v>45084</v>
@@ -2929,18 +2923,18 @@
         <v>56.299999999989936</v>
       </c>
       <c r="Q35" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R35" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" s="7">
         <v>45084</v>
@@ -2960,18 +2954,18 @@
         <v>17.399999999989291</v>
       </c>
       <c r="Q36" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R36" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R36" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B37" s="7">
         <v>45084</v>
@@ -3009,18 +3003,18 @@
         <v>60.800000000005028</v>
       </c>
       <c r="Q37" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R37" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R37" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" s="7">
         <v>45084</v>
@@ -3046,18 +3040,18 @@
         <v>18.700000000002603</v>
       </c>
       <c r="Q38" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R38" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R38" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B39" s="7">
         <v>45084</v>
@@ -3077,18 +3071,18 @@
         <v>14.399999999998414</v>
       </c>
       <c r="Q39" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R39" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R39" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B40" s="7">
         <v>45084</v>
@@ -3126,18 +3120,18 @@
         <v>93.700000000004735</v>
       </c>
       <c r="Q40" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R40" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R40" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="7">
         <v>45084</v>
@@ -3169,18 +3163,18 @@
         <v>107.90000000001143</v>
       </c>
       <c r="Q41" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R41" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R41" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B42" s="7">
         <v>45084</v>
@@ -3212,18 +3206,18 @@
         <v>84.900000000004638</v>
       </c>
       <c r="Q42" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R42" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" s="7">
         <v>45084</v>
@@ -3249,18 +3243,18 @@
         <v>32.699999999988805</v>
       </c>
       <c r="Q43" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R43" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R43" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B44" s="7">
         <v>45084</v>
@@ -3286,18 +3280,18 @@
         <v>49.200000000005772</v>
       </c>
       <c r="Q44" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R44" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R44" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" s="7">
         <v>45090</v>
@@ -3316,18 +3310,18 @@
         <v>9.4</v>
       </c>
       <c r="Q45" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R45" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R45" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B46" s="7">
         <v>45090</v>
@@ -3347,18 +3341,18 @@
         <v>9.599999999999941</v>
       </c>
       <c r="Q46" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R46" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R46" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B47" s="7">
         <v>45090</v>
@@ -3372,18 +3366,18 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R47" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R47" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S47" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" s="7">
         <v>45090</v>
@@ -3409,18 +3403,18 @@
         <v>12.200000000000788</v>
       </c>
       <c r="Q48" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R48" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R48" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" s="7">
         <v>45091</v>
@@ -3470,18 +3464,18 @@
         <v>27.499999999993108</v>
       </c>
       <c r="Q49" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R49" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R49" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B50" s="7">
         <v>45091</v>
@@ -3501,18 +3495,18 @@
         <v>9.2000000000027171</v>
       </c>
       <c r="Q50" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R50" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R50" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B51" s="7">
         <v>45097</v>
@@ -3538,18 +3532,18 @@
         <v>56.699999999992556</v>
       </c>
       <c r="Q51" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R51" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R51" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B52" s="7">
         <v>45097</v>
@@ -3569,18 +3563,18 @@
         <v>11.100000000000776</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B53" s="7">
         <v>45097</v>
@@ -3606,18 +3600,18 @@
         <v>28.100000000006631</v>
       </c>
       <c r="Q53" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R53" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R53" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B54" s="7">
         <v>45098</v>
@@ -3637,18 +3631,18 @@
         <v>12.899999999993383</v>
       </c>
       <c r="Q54" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R54" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R54" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B55" s="7">
         <v>45098</v>
@@ -3668,18 +3662,18 @@
         <v>2.5000000000019895</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B56" s="7">
         <v>45098</v>
@@ -3699,18 +3693,18 @@
         <v>3.6000000000043997</v>
       </c>
       <c r="Q56" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R56" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R56" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S56" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B57" s="7">
         <v>45098</v>
@@ -3736,18 +3730,18 @@
         <v>9.7999999999970555</v>
       </c>
       <c r="Q57" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R57" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R57" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B58" s="7">
         <v>45098</v>
@@ -3767,18 +3761,18 @@
         <v>25.000000000010303</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B59" s="7">
         <v>45098</v>
@@ -3816,18 +3810,18 @@
         <v>26.999999999975444</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B60" s="7">
         <v>45098</v>
@@ -3847,18 +3841,18 @@
         <v>12.400000000004496</v>
       </c>
       <c r="Q60" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R60" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R60" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B61" s="7">
         <v>45098</v>
@@ -3884,18 +3878,18 @@
         <v>18.909999999999634</v>
       </c>
       <c r="Q61" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R61" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R61" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S61" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B62" s="7">
         <v>45098</v>
@@ -3915,18 +3909,18 @@
         <v>15.200000000000058</v>
       </c>
       <c r="Q62" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R62" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R62" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S62" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B63" s="7">
         <v>45098</v>
@@ -3952,18 +3946,18 @@
         <v>73.600000000001359</v>
       </c>
       <c r="Q63" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R63" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R63" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S63" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B64" s="7">
         <v>45098</v>
@@ -3983,18 +3977,18 @@
         <v>8.100000000000307</v>
       </c>
       <c r="Q64" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R64" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R64" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B65" s="7">
         <v>45098</v>
@@ -4020,18 +4014,18 @@
         <v>15.899999999998649</v>
       </c>
       <c r="Q65" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R65" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R65" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S65" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B66" s="7">
         <v>45098</v>
@@ -4051,13 +4045,13 @@
         <v>6.8999999999996398</v>
       </c>
       <c r="Q66" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R66" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R66" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S66" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4083,26 +4077,26 @@
         <v>0</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R67" s="6"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P68" s="12">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R68" s="1"/>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B69" s="7">
         <v>45076</v>
@@ -4116,18 +4110,18 @@
         <v>0</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S69" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B70" s="7">
         <v>45076</v>
@@ -4141,18 +4135,18 @@
         <v>0</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S70" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B71" s="7">
         <v>45076</v>
@@ -4166,18 +4160,18 @@
         <v>0</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S71" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B72" s="7">
         <v>45076</v>
@@ -4191,18 +4185,18 @@
         <v>0</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S72" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B73" s="7">
         <v>45076</v>
@@ -4216,18 +4210,18 @@
         <v>0</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B74" s="7">
         <v>45076</v>
@@ -4241,18 +4235,18 @@
         <v>0</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S74" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B75" s="7">
         <v>45076</v>
@@ -4266,18 +4260,18 @@
         <v>0</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S75" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B76" s="7">
         <v>45076</v>
@@ -4291,18 +4285,18 @@
         <v>0</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S76" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B77" s="7">
         <v>45076</v>
@@ -4316,18 +4310,18 @@
         <v>0</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S77" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B78" s="7">
         <v>45076</v>
@@ -4341,18 +4335,18 @@
         <v>0</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S78" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B79" s="7">
         <v>45076</v>
@@ -4366,18 +4360,18 @@
         <v>0</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S79" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B80" s="7">
         <v>45076</v>
@@ -4391,18 +4385,18 @@
         <v>0</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S80" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B81" s="7">
         <v>45076</v>
@@ -4416,18 +4410,18 @@
         <v>0</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S81" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B82" s="7">
         <v>45076</v>
@@ -4441,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S82" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B83" s="7">
         <v>45076</v>
@@ -4466,18 +4460,18 @@
         <v>0</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S83" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B84" s="7">
         <v>45076</v>
@@ -4491,18 +4485,18 @@
         <v>0</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S84" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B85" s="7">
         <v>45076</v>
@@ -4516,18 +4510,18 @@
         <v>0</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S85" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B86" s="7">
         <v>45076</v>
@@ -4541,18 +4535,18 @@
         <v>0</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S86" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B87" s="7">
         <v>45076</v>
@@ -4566,18 +4560,18 @@
         <v>0</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S87" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B88" s="7">
         <v>45076</v>
@@ -4591,18 +4585,18 @@
         <v>0</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S88" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B89" s="7">
         <v>45076</v>
@@ -4616,18 +4610,18 @@
         <v>0</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S89" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B90" s="7">
         <v>45076</v>
@@ -4641,18 +4635,18 @@
         <v>0</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S90" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B91" s="7">
         <v>45076</v>
@@ -4666,18 +4660,18 @@
         <v>0</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S91" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B92" s="7">
         <v>45076</v>
@@ -4691,18 +4685,18 @@
         <v>0</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S92" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B93" s="7">
         <v>45076</v>
@@ -4716,18 +4710,18 @@
         <v>0</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S93" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B94" s="7">
         <v>45076</v>
@@ -4741,18 +4735,18 @@
         <v>0</v>
       </c>
       <c r="Q94" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S94" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B95" s="7">
         <v>45076</v>
@@ -4766,18 +4760,18 @@
         <v>0</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S95" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B96" s="7">
         <v>45076</v>
@@ -4791,18 +4785,18 @@
         <v>0</v>
       </c>
       <c r="Q96" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S96" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B97" s="7">
         <v>45076</v>
@@ -4816,18 +4810,18 @@
         <v>0</v>
       </c>
       <c r="Q97" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S97" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B98" s="7">
         <v>45076</v>
@@ -4841,18 +4835,18 @@
         <v>0</v>
       </c>
       <c r="Q98" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S98" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B99" s="7">
         <v>45076</v>
@@ -4866,18 +4860,18 @@
         <v>0</v>
       </c>
       <c r="Q99" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S99" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B100" s="7">
         <v>45076</v>
@@ -4891,18 +4885,18 @@
         <v>0</v>
       </c>
       <c r="Q100" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S100" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B101" s="7">
         <v>45076</v>
@@ -4916,18 +4910,18 @@
         <v>0</v>
       </c>
       <c r="Q101" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S101" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B102" s="7">
         <v>45076</v>
@@ -4941,18 +4935,18 @@
         <v>0</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S102" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B103" s="7">
         <v>45077</v>
@@ -4966,18 +4960,18 @@
         <v>0</v>
       </c>
       <c r="Q103" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S103" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B104" s="7">
         <v>45077</v>
@@ -4991,18 +4985,18 @@
         <v>0</v>
       </c>
       <c r="Q104" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S104" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B105" s="7">
         <v>45077</v>
@@ -5016,18 +5010,18 @@
         <v>0</v>
       </c>
       <c r="Q105" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S105" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B106" s="7">
         <v>45077</v>
@@ -5041,18 +5035,18 @@
         <v>0</v>
       </c>
       <c r="Q106" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S106" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B107" s="7">
         <v>45077</v>
@@ -5066,18 +5060,18 @@
         <v>0</v>
       </c>
       <c r="Q107" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S107" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B108" s="7">
         <v>45077</v>
@@ -5091,18 +5085,18 @@
         <v>0</v>
       </c>
       <c r="Q108" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S108" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B109" s="7">
         <v>45077</v>
@@ -5116,18 +5110,18 @@
         <v>0</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S109" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B110" s="7">
         <v>45077</v>
@@ -5141,18 +5135,18 @@
         <v>0</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S110" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B111" s="7">
         <v>45077</v>
@@ -5172,18 +5166,18 @@
         <v>15.300000000009106</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B112" s="7">
         <v>45077</v>
@@ -5197,18 +5191,18 @@
         <v>0</v>
       </c>
       <c r="Q112" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S112" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B113" s="7">
         <v>45077</v>
@@ -5222,18 +5216,18 @@
         <v>0</v>
       </c>
       <c r="Q113" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S113" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B114" s="7">
         <v>45077</v>
@@ -5247,18 +5241,18 @@
         <v>0</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S114" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B115" s="7">
         <v>45077</v>
@@ -5272,18 +5266,18 @@
         <v>0</v>
       </c>
       <c r="Q115" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S115" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B116" s="7">
         <v>45077</v>
@@ -5297,18 +5291,18 @@
         <v>0</v>
       </c>
       <c r="Q116" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S116" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B117" s="7">
         <v>45077</v>
@@ -5322,18 +5316,18 @@
         <v>0</v>
       </c>
       <c r="Q117" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S117" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B118" s="7">
         <v>45077</v>
@@ -5347,18 +5341,18 @@
         <v>0</v>
       </c>
       <c r="Q118" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S118" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B119" s="7">
         <v>45077</v>
@@ -5378,18 +5372,18 @@
         <v>167.4999999999996</v>
       </c>
       <c r="Q119" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S119" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B120" s="7">
         <v>45077</v>
@@ -5415,18 +5409,18 @@
         <v>145.4000000000002</v>
       </c>
       <c r="Q120" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R120" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S120" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B121" s="7">
         <v>45077</v>
@@ -5452,18 +5446,18 @@
         <v>99.400000000000716</v>
       </c>
       <c r="Q121" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S121" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B122" s="7">
         <v>45077</v>
@@ -5477,18 +5471,18 @@
         <v>0</v>
       </c>
       <c r="Q122" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S122" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B123" s="7">
         <v>45077</v>
@@ -5502,18 +5496,18 @@
         <v>0</v>
       </c>
       <c r="Q123" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B124" s="7">
         <v>45077</v>
@@ -5527,18 +5521,18 @@
         <v>0</v>
       </c>
       <c r="Q124" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S124" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B125" s="7">
         <v>45077</v>
@@ -5552,18 +5546,18 @@
         <v>0</v>
       </c>
       <c r="Q125" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R125" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S125" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B126" s="7">
         <v>45077</v>
@@ -5577,18 +5571,18 @@
         <v>0</v>
       </c>
       <c r="Q126" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S126" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B127" s="7">
         <v>45077</v>
@@ -5602,18 +5596,18 @@
         <v>0</v>
       </c>
       <c r="Q127" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R127" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S127" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B128" s="7">
         <v>45077</v>
@@ -5627,18 +5621,18 @@
         <v>0</v>
       </c>
       <c r="Q128" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R128" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S128" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B129" s="7">
         <v>45077</v>
@@ -5652,18 +5646,18 @@
         <v>0</v>
       </c>
       <c r="Q129" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S129" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B130" s="7">
         <v>45077</v>
@@ -5677,18 +5671,18 @@
         <v>0</v>
       </c>
       <c r="Q130" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S130" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B131" s="7">
         <v>45077</v>
@@ -5702,18 +5696,18 @@
         <v>0</v>
       </c>
       <c r="Q131" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S131" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B132" s="7">
         <v>45077</v>
@@ -5727,18 +5721,18 @@
         <v>0</v>
       </c>
       <c r="Q132" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S132" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B133" s="7">
         <v>45077</v>
@@ -5752,18 +5746,18 @@
         <v>0</v>
       </c>
       <c r="Q133" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S133" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B134" s="7">
         <v>45077</v>
@@ -5777,18 +5771,18 @@
         <v>0</v>
       </c>
       <c r="Q134" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S134" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B135" s="7">
         <v>45077</v>
@@ -5808,18 +5802,18 @@
         <v>27.299999999998992</v>
       </c>
       <c r="Q135" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R135" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S135" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B136" s="7">
         <v>45077</v>
@@ -5833,18 +5827,18 @@
         <v>0</v>
       </c>
       <c r="Q136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S136" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B137" s="7">
         <v>45077</v>
@@ -5858,18 +5852,18 @@
         <v>0</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R137" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S137" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B138" s="7">
         <v>45077</v>
@@ -5883,18 +5877,18 @@
         <v>0</v>
       </c>
       <c r="Q138" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S138" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B139" s="7">
         <v>45077</v>
@@ -5908,18 +5902,18 @@
         <v>0</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S139" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B140" s="7">
         <v>45077</v>
@@ -5933,18 +5927,18 @@
         <v>0</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S140" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B141" s="7">
         <v>45077</v>
@@ -5958,18 +5952,18 @@
         <v>0</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S141" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B142" s="7">
         <v>45083</v>
@@ -5983,18 +5977,18 @@
         <v>0</v>
       </c>
       <c r="Q142" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R142" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S142" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B143" s="7">
         <v>45083</v>
@@ -6008,18 +6002,18 @@
         <v>0</v>
       </c>
       <c r="Q143" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S143" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B144" s="7">
         <v>45083</v>
@@ -6033,18 +6027,18 @@
         <v>0</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R144" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S144" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B145" s="7">
         <v>45083</v>
@@ -6058,18 +6052,18 @@
         <v>0</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R145" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S145" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B146" s="7">
         <v>45083</v>
@@ -6083,18 +6077,18 @@
         <v>0</v>
       </c>
       <c r="Q146" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S146" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B147" s="7">
         <v>45083</v>
@@ -6108,18 +6102,18 @@
         <v>0</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R147" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S147" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B148" s="7">
         <v>45083</v>
@@ -6133,18 +6127,18 @@
         <v>0</v>
       </c>
       <c r="Q148" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R148" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S148" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B149" s="7">
         <v>45083</v>
@@ -6158,18 +6152,18 @@
         <v>0</v>
       </c>
       <c r="Q149" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R149" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S149" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B150" s="7">
         <v>45083</v>
@@ -6183,18 +6177,18 @@
         <v>0</v>
       </c>
       <c r="Q150" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S150" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B151" s="7">
         <v>45083</v>
@@ -6208,18 +6202,18 @@
         <v>0</v>
       </c>
       <c r="Q151" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S151" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B152" s="7">
         <v>45083</v>
@@ -6233,18 +6227,18 @@
         <v>0</v>
       </c>
       <c r="Q152" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S152" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B153" s="7">
         <v>45083</v>
@@ -6258,18 +6252,18 @@
         <v>0</v>
       </c>
       <c r="Q153" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S153" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B154" s="7">
         <v>45083</v>
@@ -6283,18 +6277,18 @@
         <v>0</v>
       </c>
       <c r="Q154" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R154" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S154" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B155" s="7">
         <v>45083</v>
@@ -6308,18 +6302,18 @@
         <v>0</v>
       </c>
       <c r="Q155" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S155" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B156" s="7">
         <v>45083</v>
@@ -6339,18 +6333,18 @@
         <v>187.9999999999996</v>
       </c>
       <c r="Q156" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S156" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B157" s="7">
         <v>45083</v>
@@ -6364,18 +6358,18 @@
         <v>0</v>
       </c>
       <c r="Q157" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S157" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B158" s="7">
         <v>45083</v>
@@ -6389,18 +6383,18 @@
         <v>0</v>
       </c>
       <c r="Q158" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S158" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B159" s="7">
         <v>45083</v>
@@ -6414,18 +6408,18 @@
         <v>0</v>
       </c>
       <c r="Q159" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S159" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B160" s="7">
         <v>45083</v>
@@ -6439,18 +6433,18 @@
         <v>0</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S160" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B161" s="7">
         <v>45083</v>
@@ -6464,18 +6458,18 @@
         <v>0</v>
       </c>
       <c r="Q161" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R161" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S161" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B162" s="7">
         <v>45083</v>
@@ -6489,18 +6483,18 @@
         <v>0</v>
       </c>
       <c r="Q162" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R162" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S162" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B163" s="7">
         <v>45083</v>
@@ -6514,18 +6508,18 @@
         <v>0</v>
       </c>
       <c r="Q163" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R163" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S163" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B164" s="7">
         <v>45083</v>
@@ -6539,18 +6533,18 @@
         <v>0</v>
       </c>
       <c r="Q164" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R164" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S164" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B165" s="7">
         <v>45083</v>
@@ -6564,18 +6558,18 @@
         <v>0</v>
       </c>
       <c r="Q165" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S165" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B166" s="7">
         <v>45083</v>
@@ -6589,18 +6583,18 @@
         <v>0</v>
       </c>
       <c r="Q166" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R166" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S166" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B167" s="7">
         <v>45083</v>
@@ -6614,18 +6608,18 @@
         <v>0</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S167" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B168" s="7">
         <v>45084</v>
@@ -6639,18 +6633,18 @@
         <v>0</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S168" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B169" s="7">
         <v>45084</v>
@@ -6664,18 +6658,18 @@
         <v>0</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S169" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B170" s="7">
         <v>45084</v>
@@ -6689,18 +6683,18 @@
         <v>0</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R170" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S170" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B171" s="7">
         <v>45084</v>
@@ -6714,18 +6708,18 @@
         <v>0</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R171" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S171" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B172" s="7">
         <v>45084</v>
@@ -6739,18 +6733,18 @@
         <v>0</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S172" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B173" s="7">
         <v>45084</v>
@@ -6764,18 +6758,18 @@
         <v>0</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R173" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S173" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B174" s="7">
         <v>45084</v>
@@ -6789,18 +6783,18 @@
         <v>0</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R174" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S174" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B175" s="7">
         <v>45084</v>
@@ -6814,18 +6808,18 @@
         <v>0</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R175" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S175" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B176" s="7">
         <v>45084</v>
@@ -6839,18 +6833,18 @@
         <v>0</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R176" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S176" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B177" s="7">
         <v>45084</v>
@@ -6864,18 +6858,18 @@
         <v>0</v>
       </c>
       <c r="Q177" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R177" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S177" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B178" s="7">
         <v>45084</v>
@@ -6889,18 +6883,18 @@
         <v>0</v>
       </c>
       <c r="Q178" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R178" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S178" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B179" s="7">
         <v>45084</v>
@@ -6914,18 +6908,18 @@
         <v>0</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R179" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S179" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B180" s="7">
         <v>45084</v>
@@ -6939,18 +6933,18 @@
         <v>0</v>
       </c>
       <c r="Q180" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R180" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S180" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B181" s="7">
         <v>45084</v>
@@ -6964,18 +6958,18 @@
         <v>0</v>
       </c>
       <c r="Q181" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R181" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S181" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B182" s="7">
         <v>45084</v>
@@ -6989,18 +6983,18 @@
         <v>0</v>
       </c>
       <c r="Q182" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R182" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S182" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B183" s="7">
         <v>45084</v>
@@ -7014,18 +7008,18 @@
         <v>0</v>
       </c>
       <c r="Q183" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R183" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S183" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B184" s="7">
         <v>45084</v>
@@ -7045,18 +7039,18 @@
         <v>41.799999999995663</v>
       </c>
       <c r="Q184" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S184" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B185" s="7">
         <v>45084</v>
@@ -7076,18 +7070,18 @@
         <v>30.500000000012761</v>
       </c>
       <c r="Q185" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R185" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="S185" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B186" s="7">
         <v>45084</v>
@@ -7101,18 +7095,18 @@
         <v>0</v>
       </c>
       <c r="Q186" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R186" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S186" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B187" s="7">
         <v>45084</v>
@@ -7126,18 +7120,18 @@
         <v>0</v>
       </c>
       <c r="Q187" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R187" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S187" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B188" s="7">
         <v>45084</v>
@@ -7157,18 +7151,18 @@
         <v>4.4000000000000483</v>
       </c>
       <c r="Q188" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R188" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R188" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S188" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B189" s="7">
         <v>45084</v>
@@ -7182,18 +7176,18 @@
         <v>0</v>
       </c>
       <c r="Q189" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R189" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S189" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B190" s="7">
         <v>45084</v>
@@ -7207,18 +7201,18 @@
         <v>0</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R190" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S190" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B191" s="7">
         <v>45090</v>
@@ -7232,18 +7226,18 @@
         <v>0</v>
       </c>
       <c r="Q191" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R191" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S191" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B192" s="7">
         <v>45090</v>
@@ -7257,18 +7251,18 @@
         <v>0</v>
       </c>
       <c r="Q192" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R192" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S192" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B193" s="7">
         <v>45090</v>
@@ -7282,18 +7276,18 @@
         <v>0</v>
       </c>
       <c r="Q193" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R193" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S193" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B194" s="7">
         <v>45090</v>
@@ -7307,18 +7301,18 @@
         <v>0</v>
       </c>
       <c r="Q194" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R194" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S194" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B195" s="7">
         <v>45090</v>
@@ -7332,18 +7326,18 @@
         <v>0</v>
       </c>
       <c r="Q195" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R195" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S195" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B196" s="7">
         <v>45090</v>
@@ -7357,18 +7351,18 @@
         <v>0</v>
       </c>
       <c r="Q196" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R196" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S196" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B197" s="7">
         <v>45090</v>
@@ -7382,18 +7376,18 @@
         <v>0</v>
       </c>
       <c r="Q197" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R197" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S197" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B198" s="7">
         <v>45090</v>
@@ -7407,18 +7401,18 @@
         <v>0</v>
       </c>
       <c r="Q198" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R198" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S198" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B199" s="7">
         <v>45090</v>
@@ -7432,18 +7426,18 @@
         <v>0</v>
       </c>
       <c r="Q199" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R199" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S199" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B200" s="7">
         <v>45090</v>
@@ -7457,18 +7451,18 @@
         <v>0</v>
       </c>
       <c r="Q200" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R200" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S200" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B201" s="7">
         <v>45090</v>
@@ -7482,18 +7476,18 @@
         <v>0</v>
       </c>
       <c r="Q201" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R201" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S201" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B202" s="7">
         <v>45090</v>
@@ -7507,18 +7501,18 @@
         <v>0</v>
       </c>
       <c r="Q202" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R202" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S202" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B203" s="7">
         <v>45090</v>
@@ -7532,18 +7526,18 @@
         <v>0</v>
       </c>
       <c r="Q203" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R203" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S203" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B204" s="7">
         <v>45090</v>
@@ -7557,18 +7551,18 @@
         <v>0</v>
       </c>
       <c r="Q204" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R204" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S204" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B205" s="7">
         <v>45090</v>
@@ -7582,18 +7576,18 @@
         <v>0</v>
       </c>
       <c r="Q205" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R205" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S205" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B206" s="7">
         <v>45090</v>
@@ -7607,18 +7601,18 @@
         <v>0</v>
       </c>
       <c r="Q206" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R206" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S206" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B207" s="7">
         <v>45090</v>
@@ -7632,18 +7626,18 @@
         <v>0</v>
       </c>
       <c r="Q207" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R207" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S207" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B208" s="7">
         <v>45090</v>
@@ -7657,18 +7651,18 @@
         <v>0</v>
       </c>
       <c r="Q208" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R208" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S208" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B209" s="7">
         <v>45090</v>
@@ -7682,18 +7676,18 @@
         <v>0</v>
       </c>
       <c r="Q209" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R209" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S209" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B210" s="7">
         <v>45090</v>
@@ -7707,18 +7701,18 @@
         <v>0</v>
       </c>
       <c r="Q210" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R210" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S210" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B211" s="7">
         <v>45090</v>
@@ -7732,18 +7726,18 @@
         <v>0</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S211" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B212" s="7">
         <v>45090</v>
@@ -7757,18 +7751,18 @@
         <v>0</v>
       </c>
       <c r="Q212" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R212" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S212" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B213" s="7">
         <v>45090</v>
@@ -7782,18 +7776,18 @@
         <v>0</v>
       </c>
       <c r="Q213" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R213" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S213" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B214" s="7">
         <v>45090</v>
@@ -7807,18 +7801,18 @@
         <v>0</v>
       </c>
       <c r="Q214" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R214" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S214" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B215" s="7">
         <v>45090</v>
@@ -7832,18 +7826,18 @@
         <v>0</v>
       </c>
       <c r="Q215" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R215" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S215" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B216" s="7">
         <v>45090</v>
@@ -7857,18 +7851,18 @@
         <v>0</v>
       </c>
       <c r="Q216" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R216" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S216" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B217" s="7">
         <v>45090</v>
@@ -7882,18 +7876,18 @@
         <v>0</v>
       </c>
       <c r="Q217" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R217" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S217" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B218" s="7">
         <v>45090</v>
@@ -7907,18 +7901,18 @@
         <v>0</v>
       </c>
       <c r="Q218" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R218" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S218" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B219" s="7">
         <v>45090</v>
@@ -7932,18 +7926,18 @@
         <v>0</v>
       </c>
       <c r="Q219" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R219" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S219" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B220" s="7">
         <v>45090</v>
@@ -7957,18 +7951,18 @@
         <v>0</v>
       </c>
       <c r="Q220" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R220" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S220" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B221" s="7">
         <v>45090</v>
@@ -7982,18 +7976,18 @@
         <v>0</v>
       </c>
       <c r="Q221" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R221" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S221" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B222" s="7">
         <v>45090</v>
@@ -8007,18 +8001,18 @@
         <v>0</v>
       </c>
       <c r="Q222" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R222" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S222" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B223" s="7">
         <v>45090</v>
@@ -8032,18 +8026,18 @@
         <v>0</v>
       </c>
       <c r="Q223" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R223" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S223" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B224" s="7">
         <v>45090</v>
@@ -8057,18 +8051,18 @@
         <v>0</v>
       </c>
       <c r="Q224" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R224" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S224" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B225" s="7">
         <v>45090</v>
@@ -8082,18 +8076,18 @@
         <v>0</v>
       </c>
       <c r="Q225" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R225" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S225" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B226" s="7">
         <v>45090</v>
@@ -8107,18 +8101,18 @@
         <v>0</v>
       </c>
       <c r="Q226" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R226" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S226" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B227" s="7">
         <v>45090</v>
@@ -8132,18 +8126,18 @@
         <v>0</v>
       </c>
       <c r="Q227" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R227" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S227" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B228" s="7">
         <v>45090</v>
@@ -8157,18 +8151,18 @@
         <v>0</v>
       </c>
       <c r="Q228" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R228" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S228" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B229" s="7">
         <v>45090</v>
@@ -8182,18 +8176,18 @@
         <v>0</v>
       </c>
       <c r="Q229" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R229" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S229" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B230" s="7">
         <v>45090</v>
@@ -8207,18 +8201,18 @@
         <v>0</v>
       </c>
       <c r="Q230" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R230" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S230" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B231" s="7">
         <v>45090</v>
@@ -8232,18 +8226,18 @@
         <v>0</v>
       </c>
       <c r="Q231" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R231" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S231" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B232" s="7">
         <v>45090</v>
@@ -8257,18 +8251,18 @@
         <v>0</v>
       </c>
       <c r="Q232" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R232" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S232" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B233" s="7">
         <v>45090</v>
@@ -8282,18 +8276,18 @@
         <v>0</v>
       </c>
       <c r="Q233" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R233" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S233" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B234" s="7">
         <v>45090</v>
@@ -8307,18 +8301,18 @@
         <v>0</v>
       </c>
       <c r="Q234" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R234" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S234" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B235" s="7">
         <v>45090</v>
@@ -8332,18 +8326,18 @@
         <v>0</v>
       </c>
       <c r="Q235" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S235" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B236" s="7">
         <v>45090</v>
@@ -8357,18 +8351,18 @@
         <v>0</v>
       </c>
       <c r="Q236" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R236" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S236" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B237" s="7">
         <v>45091</v>
@@ -8382,18 +8376,18 @@
         <v>0</v>
       </c>
       <c r="Q237" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R237" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S237" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B238" s="7">
         <v>45091</v>
@@ -8413,18 +8407,18 @@
         <v>4.4999999999959073</v>
       </c>
       <c r="Q238" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R238" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R238" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S238" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B239" s="7">
         <v>45091</v>
@@ -8444,18 +8438,18 @@
         <v>4.7999999999930765</v>
       </c>
       <c r="Q239" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R239" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R239" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S239" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B240" s="7">
         <v>45091</v>
@@ -8481,18 +8475,18 @@
         <v>10.599999999992704</v>
       </c>
       <c r="Q240" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R240" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R240" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S240" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B241" s="7">
         <v>45091</v>
@@ -8506,18 +8500,18 @@
         <v>0</v>
       </c>
       <c r="Q241" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R241" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S241" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B242" s="7">
         <v>45091</v>
@@ -8531,18 +8525,18 @@
         <v>0</v>
       </c>
       <c r="Q242" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R242" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S242" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B243" s="7">
         <v>45091</v>
@@ -8556,18 +8550,18 @@
         <v>0</v>
       </c>
       <c r="Q243" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R243" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S243" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B244" s="7">
         <v>45091</v>
@@ -8581,18 +8575,18 @@
         <v>0</v>
       </c>
       <c r="Q244" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R244" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S244" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B245" s="7">
         <v>45091</v>
@@ -8606,18 +8600,18 @@
         <v>0</v>
       </c>
       <c r="Q245" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R245" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S245" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B246" s="7">
         <v>45091</v>
@@ -8631,18 +8625,18 @@
         <v>0</v>
       </c>
       <c r="Q246" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R246" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S246" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B247" s="7">
         <v>45091</v>
@@ -8656,18 +8650,18 @@
         <v>0</v>
       </c>
       <c r="Q247" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R247" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S247" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B248" s="7">
         <v>45091</v>
@@ -8681,18 +8675,18 @@
         <v>0</v>
       </c>
       <c r="Q248" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R248" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S248" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B249" s="7">
         <v>45091</v>
@@ -8706,18 +8700,18 @@
         <v>0</v>
       </c>
       <c r="Q249" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R249" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S249" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B250" s="7">
         <v>45091</v>
@@ -8731,18 +8725,18 @@
         <v>0</v>
       </c>
       <c r="Q250" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R250" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S250" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B251" s="7">
         <v>45091</v>
@@ -8756,18 +8750,18 @@
         <v>0</v>
       </c>
       <c r="Q251" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R251" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S251" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B252" s="7">
         <v>45091</v>
@@ -8781,18 +8775,18 @@
         <v>0</v>
       </c>
       <c r="Q252" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R252" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S252" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B253" s="7">
         <v>45091</v>
@@ -8806,18 +8800,18 @@
         <v>0</v>
       </c>
       <c r="Q253" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R253" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S253" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B254" s="7">
         <v>45091</v>
@@ -8831,18 +8825,18 @@
         <v>0</v>
       </c>
       <c r="Q254" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R254" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S254" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B255" s="7">
         <v>45091</v>
@@ -8856,18 +8850,18 @@
         <v>0</v>
       </c>
       <c r="Q255" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R255" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S255" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B256" s="7">
         <v>45091</v>
@@ -8881,18 +8875,18 @@
         <v>0</v>
       </c>
       <c r="Q256" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R256" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S256" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B257" s="7">
         <v>45091</v>
@@ -8906,18 +8900,18 @@
         <v>0</v>
       </c>
       <c r="Q257" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R257" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S257" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B258" s="7">
         <v>45091</v>
@@ -8931,18 +8925,18 @@
         <v>0</v>
       </c>
       <c r="Q258" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R258" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S258" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B259" s="7">
         <v>45091</v>
@@ -8956,18 +8950,18 @@
         <v>0</v>
       </c>
       <c r="Q259" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R259" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S259" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B260" s="7">
         <v>45091</v>
@@ -8981,18 +8975,18 @@
         <v>0</v>
       </c>
       <c r="Q260" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S260" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B261" s="7">
         <v>45091</v>
@@ -9006,18 +9000,18 @@
         <v>0</v>
       </c>
       <c r="Q261" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S261" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B262" s="7">
         <v>45091</v>
@@ -9031,18 +9025,18 @@
         <v>0</v>
       </c>
       <c r="Q262" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S262" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B263" s="7">
         <v>45091</v>
@@ -9056,18 +9050,18 @@
         <v>0</v>
       </c>
       <c r="Q263" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S263" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B264" s="7">
         <v>45091</v>
@@ -9081,18 +9075,18 @@
         <v>0</v>
       </c>
       <c r="Q264" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R264" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S264" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B265" s="7">
         <v>45091</v>
@@ -9106,18 +9100,18 @@
         <v>0</v>
       </c>
       <c r="Q265" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S265" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B266" s="7">
         <v>45091</v>
@@ -9131,18 +9125,18 @@
         <v>0</v>
       </c>
       <c r="Q266" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S266" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B267" s="7">
         <v>45091</v>
@@ -9156,18 +9150,18 @@
         <v>0</v>
       </c>
       <c r="Q267" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S267" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B268" s="7">
         <v>45091</v>
@@ -9181,18 +9175,18 @@
         <v>0</v>
       </c>
       <c r="Q268" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S268" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B269" s="7">
         <v>45091</v>
@@ -9206,18 +9200,18 @@
         <v>0</v>
       </c>
       <c r="Q269" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R269" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S269" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B270" s="7">
         <v>45091</v>
@@ -9231,18 +9225,18 @@
         <v>0</v>
       </c>
       <c r="Q270" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R270" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S270" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B271" s="7">
         <v>45091</v>
@@ -9256,18 +9250,18 @@
         <v>0</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R271" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S271" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B272" s="7">
         <v>45091</v>
@@ -9281,18 +9275,18 @@
         <v>0</v>
       </c>
       <c r="Q272" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R272" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S272" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B273" s="7">
         <v>45091</v>
@@ -9306,18 +9300,18 @@
         <v>0</v>
       </c>
       <c r="Q273" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R273" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S273" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B274" s="7">
         <v>45091</v>
@@ -9331,18 +9325,18 @@
         <v>0</v>
       </c>
       <c r="Q274" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R274" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S274" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B275" s="7">
         <v>45097</v>
@@ -9356,18 +9350,18 @@
         <v>0</v>
       </c>
       <c r="Q275" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R275" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S275" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B276" s="7">
         <v>45097</v>
@@ -9381,18 +9375,18 @@
         <v>0</v>
       </c>
       <c r="Q276" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S276" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B277" s="7">
         <v>45097</v>
@@ -9406,18 +9400,18 @@
         <v>0</v>
       </c>
       <c r="Q277" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R277" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S277" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B278" s="7">
         <v>45097</v>
@@ -9431,18 +9425,18 @@
         <v>0</v>
       </c>
       <c r="Q278" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R278" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S278" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B279" s="7">
         <v>45097</v>
@@ -9456,18 +9450,18 @@
         <v>0</v>
       </c>
       <c r="Q279" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R279" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S279" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B280" s="7">
         <v>45097</v>
@@ -9481,18 +9475,18 @@
         <v>0</v>
       </c>
       <c r="Q280" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R280" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S280" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B281" s="7">
         <v>45097</v>
@@ -9506,18 +9500,18 @@
         <v>0</v>
       </c>
       <c r="Q281" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R281" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S281" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B282" s="7">
         <v>45097</v>
@@ -9531,18 +9525,18 @@
         <v>0</v>
       </c>
       <c r="Q282" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R282" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S282" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B283" s="7">
         <v>45097</v>
@@ -9556,18 +9550,18 @@
         <v>0</v>
       </c>
       <c r="Q283" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R283" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S283" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B284" s="7">
         <v>45097</v>
@@ -9581,18 +9575,18 @@
         <v>0</v>
       </c>
       <c r="Q284" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S284" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B285" s="7">
         <v>45097</v>
@@ -9606,18 +9600,18 @@
         <v>0</v>
       </c>
       <c r="Q285" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R285" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S285" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B286" s="7">
         <v>45097</v>
@@ -9631,18 +9625,18 @@
         <v>0</v>
       </c>
       <c r="Q286" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R286" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S286" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B287" s="7">
         <v>45097</v>
@@ -9656,18 +9650,18 @@
         <v>0</v>
       </c>
       <c r="Q287" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R287" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S287" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B288" s="7">
         <v>45097</v>
@@ -9681,18 +9675,18 @@
         <v>0</v>
       </c>
       <c r="Q288" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R288" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S288" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B289" s="7">
         <v>45097</v>
@@ -9706,18 +9700,18 @@
         <v>0</v>
       </c>
       <c r="Q289" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R289" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S289" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B290" s="7">
         <v>45097</v>
@@ -9731,18 +9725,18 @@
         <v>0</v>
       </c>
       <c r="Q290" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R290" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S290" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B291" s="7">
         <v>45097</v>
@@ -9756,18 +9750,18 @@
         <v>0</v>
       </c>
       <c r="Q291" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R291" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S291" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B292" s="7">
         <v>45097</v>
@@ -9781,18 +9775,18 @@
         <v>0</v>
       </c>
       <c r="Q292" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R292" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S292" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B293" s="7">
         <v>45098</v>
@@ -9806,18 +9800,18 @@
         <v>0</v>
       </c>
       <c r="Q293" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R293" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S293" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B294" s="7">
         <v>45098</v>
@@ -9831,18 +9825,18 @@
         <v>0</v>
       </c>
       <c r="Q294" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R294" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S294" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B295" s="7">
         <v>45098</v>
@@ -9856,18 +9850,18 @@
         <v>0</v>
       </c>
       <c r="Q295" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R295" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S295" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B296" s="7">
         <v>45098</v>
@@ -9881,18 +9875,18 @@
         <v>0</v>
       </c>
       <c r="Q296" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R296" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S296" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B297" s="7">
         <v>45098</v>
@@ -9906,18 +9900,18 @@
         <v>0</v>
       </c>
       <c r="Q297" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R297" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S297" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B298" s="7">
         <v>45098</v>
@@ -9931,18 +9925,18 @@
         <v>0</v>
       </c>
       <c r="Q298" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R298" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S298" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B299" s="7">
         <v>45098</v>
@@ -9956,18 +9950,18 @@
         <v>0</v>
       </c>
       <c r="Q299" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R299" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S299" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B300" s="7">
         <v>45098</v>
@@ -9981,18 +9975,18 @@
         <v>0</v>
       </c>
       <c r="Q300" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R300" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S300" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B301" s="7">
         <v>45098</v>
@@ -10006,18 +10000,18 @@
         <v>0</v>
       </c>
       <c r="Q301" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R301" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S301" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B302" s="7">
         <v>45098</v>
@@ -10031,18 +10025,18 @@
         <v>0</v>
       </c>
       <c r="Q302" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R302" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S302" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B303" s="7">
         <v>45098</v>
@@ -10056,18 +10050,18 @@
         <v>0</v>
       </c>
       <c r="Q303" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R303" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S303" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B304" s="7">
         <v>45098</v>
@@ -10081,18 +10075,18 @@
         <v>0</v>
       </c>
       <c r="Q304" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R304" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S304" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B305" s="7">
         <v>45098</v>
@@ -10106,18 +10100,18 @@
         <v>0</v>
       </c>
       <c r="Q305" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R305" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S305" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B306" s="7">
         <v>45098</v>
@@ -10131,18 +10125,18 @@
         <v>0</v>
       </c>
       <c r="Q306" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R306" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S306" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B307" s="7">
         <v>45098</v>
@@ -10156,18 +10150,18 @@
         <v>0</v>
       </c>
       <c r="Q307" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R307" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S307" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B308" s="7">
         <v>45098</v>
@@ -10181,18 +10175,18 @@
         <v>0</v>
       </c>
       <c r="Q308" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R308" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S308" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B309" s="7">
         <v>45098</v>
@@ -10206,18 +10200,18 @@
         <v>0</v>
       </c>
       <c r="Q309" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R309" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S309" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B310" s="7">
         <v>45098</v>
@@ -10231,18 +10225,18 @@
         <v>0</v>
       </c>
       <c r="Q310" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R310" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S310" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B311" s="7">
         <v>45098</v>
@@ -10256,18 +10250,18 @@
         <v>0</v>
       </c>
       <c r="Q311" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R311" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S311" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B312" s="7">
         <v>45098</v>
@@ -10281,18 +10275,18 @@
         <v>0</v>
       </c>
       <c r="Q312" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R312" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S312" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B313" s="7">
         <v>45098</v>
@@ -10312,18 +10306,18 @@
         <v>4.1999999999999371</v>
       </c>
       <c r="Q313" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R313" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R313" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="S313" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B314" s="7">
         <v>45098</v>
@@ -10337,18 +10331,18 @@
         <v>0</v>
       </c>
       <c r="Q314" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R314" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S314" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B315" s="7">
         <v>45098</v>
@@ -10362,18 +10356,18 @@
         <v>0</v>
       </c>
       <c r="Q315" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R315" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S315" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B316" s="7">
         <v>45098</v>
@@ -10387,18 +10381,18 @@
         <v>0</v>
       </c>
       <c r="Q316" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R316" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S316" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B317" s="7">
         <v>45098</v>
@@ -10412,18 +10406,18 @@
         <v>0</v>
       </c>
       <c r="Q317" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R317" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S317" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B318" s="7">
         <v>45098</v>
@@ -10437,18 +10431,18 @@
         <v>0</v>
       </c>
       <c r="Q318" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R318" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S318" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B319" s="7">
         <v>45098</v>
@@ -10462,18 +10456,18 @@
         <v>0</v>
       </c>
       <c r="Q319" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R319" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S319" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B320" s="7">
         <v>45098</v>
@@ -10487,18 +10481,18 @@
         <v>0</v>
       </c>
       <c r="Q320" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R320" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S320" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B321" s="7">
         <v>45098</v>
@@ -10512,18 +10506,18 @@
         <v>0</v>
       </c>
       <c r="Q321" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R321" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S321" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B322" s="7">
         <v>45098</v>
@@ -10537,18 +10531,18 @@
         <v>0</v>
       </c>
       <c r="Q322" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R322" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S322" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B323" s="7">
         <v>45098</v>
@@ -10562,13 +10556,13 @@
         <v>0</v>
       </c>
       <c r="Q323" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R323" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S323" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="324" spans="1:19" x14ac:dyDescent="0.25">
